--- a/data/temp_kumite.xlsx
+++ b/data/temp_kumite.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izrantsevavs\Documents\portfolio\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A49373B-91D1-4C25-ACB1-854F1090CC77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45929A68-0472-4BF0-A66C-B2874850CF28}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18555" windowHeight="12555" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18555" windowHeight="12555" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="len1" sheetId="5" r:id="rId1"/>
     <sheet name="len2" sheetId="7" r:id="rId2"/>
     <sheet name="len3" sheetId="8" r:id="rId3"/>
     <sheet name="len4" sheetId="9" r:id="rId4"/>
+    <sheet name="len8" sheetId="10" r:id="rId5"/>
+    <sheet name="len16" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="21">
   <si>
     <t>Региональные соревнования "Северный воин"</t>
   </si>
@@ -83,6 +85,9 @@
   </si>
   <si>
     <t>1/4</t>
+  </si>
+  <si>
+    <t>1/8</t>
   </si>
 </sst>
 </file>
@@ -162,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -311,11 +316,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -404,6 +418,69 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -416,29 +493,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -449,20 +511,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -784,96 +855,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -956,11 +1027,11 @@
       <c r="C19" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="s">
@@ -969,19 +1040,19 @@
       <c r="C20" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1001,17 +1072,17 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="32" t="s">
+      <c r="H25" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
@@ -1022,15 +1093,21 @@
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
-      <c r="H27" s="32" t="s">
+      <c r="H27" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="E21:G21"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A4:B4"/>
@@ -1038,12 +1115,6 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="H4:K4"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="E21:G21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -1070,96 +1141,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -1306,18 +1377,18 @@
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
       <c r="D33" s="13"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="60"/>
       <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="8"/>
       <c r="D34" s="17"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="47"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="57"/>
       <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1339,11 +1410,11 @@
       <c r="C39" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="s">
@@ -1352,11 +1423,11 @@
       <c r="C40" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="s">
@@ -1365,11 +1436,11 @@
       <c r="C41" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" s="17"/>
@@ -1386,17 +1457,17 @@
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
-      <c r="H46" s="32" t="s">
+      <c r="H46" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
@@ -1407,15 +1478,22 @@
       <c r="E48" s="13"/>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
-      <c r="H48" s="32" t="s">
+      <c r="H48" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:K6"/>
     <mergeCell ref="D39:H39"/>
     <mergeCell ref="D40:H40"/>
     <mergeCell ref="A4:B4"/>
@@ -1424,13 +1502,6 @@
     <mergeCell ref="H46:K46"/>
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="D41:H41"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -1457,96 +1528,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:11" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -1732,11 +1803,11 @@
       <c r="C34" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="s">
@@ -1745,11 +1816,11 @@
       <c r="C35" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="s">
@@ -1758,19 +1829,19 @@
       <c r="C36" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
       <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1790,17 +1861,17 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
-      <c r="H41" s="32" t="s">
+      <c r="H41" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
@@ -1811,12 +1882,12 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
-      <c r="H43" s="32" t="s">
+      <c r="H43" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1860,96 +1931,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:12" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -2001,8 +2072,8 @@
     </row>
     <row r="11" spans="1:12" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="48"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="41"/>
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2022,7 +2093,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="48"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="27"/>
       <c r="E13" s="6"/>
       <c r="F13" s="26"/>
@@ -2190,7 +2261,7 @@
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="21"/>
       <c r="B25" s="8"/>
-      <c r="C25" s="48"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="27"/>
       <c r="E25" s="6"/>
       <c r="F25" s="8"/>
@@ -2325,18 +2396,18 @@
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
       <c r="D36" s="13"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="60"/>
       <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
       <c r="C37" s="8"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="47"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="57"/>
       <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2358,11 +2429,11 @@
       <c r="C42" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="s">
@@ -2371,11 +2442,11 @@
       <c r="C43" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="s">
@@ -2384,11 +2455,11 @@
       <c r="C44" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" s="18"/>
@@ -2417,17 +2488,17 @@
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
-      <c r="H49" s="32" t="s">
+      <c r="H49" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="52"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
@@ -2438,21 +2509,15 @@
       <c r="E51" s="13"/>
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
-      <c r="H51" s="32" t="s">
+      <c r="H51" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="H51:K51"/>
@@ -2462,8 +2527,2456 @@
     <mergeCell ref="D42:H42"/>
     <mergeCell ref="D43:H43"/>
     <mergeCell ref="D44:H44"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E349A5-B6C4-4810-A1D6-16DB5CC77CEA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="30"/>
+    <col min="2" max="2" width="31.28515625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="30"/>
+    <col min="4" max="4" width="5.7109375" style="30" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="30" customWidth="1"/>
+    <col min="6" max="7" width="4.28515625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" style="30" customWidth="1"/>
+    <col min="9" max="10" width="4.28515625" style="30" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" style="30" customWidth="1"/>
+    <col min="12" max="13" width="4.28515625" style="30" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" style="30" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+    </row>
+    <row r="2" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+    </row>
+    <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+    </row>
+    <row r="4" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D7" s="2"/>
+      <c r="E7" s="32"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D9" s="2"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D10" s="2"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="42"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="8"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C16" s="32"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="6"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D22" s="2"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="6"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="8"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C28" s="32"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="6"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="8"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" s="42"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+      <c r="O30" s="32"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" s="6"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" s="8"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="38"/>
+      <c r="O32" s="32"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="32"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="32"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="8"/>
+      <c r="O35" s="32"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B36" s="42"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" s="6"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="8"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C40" s="32"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="6"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="42"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+      <c r="C43" s="8"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="8"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B47" s="6"/>
+      <c r="C47" s="38"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="8"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="42"/>
+      <c r="C48" s="41"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B49" s="6"/>
+      <c r="C49" s="8"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" s="8"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C52" s="32"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B53" s="6"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="40"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="42"/>
+      <c r="C54" s="41"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B55" s="6"/>
+      <c r="C55" s="8"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B56" s="8"/>
+      <c r="C56" s="35"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="N57" s="32"/>
+      <c r="O57" s="32"/>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="32"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B60" s="6"/>
+      <c r="C60" s="38"/>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
+      <c r="N60" s="32"/>
+      <c r="O60" s="32"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B61" s="38"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="32"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B62" s="35"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="32"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B63" s="8"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B64" s="32"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B65" s="32"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B66" s="32"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B67" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B68" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="51"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="51"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B69" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="51"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B70" s="18"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B71" s="18"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="H76:K76"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="H74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="K4:N4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="57" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97CD645-51CD-4DE3-A8AD-46DA073A142F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:W76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="30"/>
+    <col min="2" max="2" width="31.28515625" style="30" customWidth="1"/>
+    <col min="3" max="4" width="4.28515625" style="30" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="30" customWidth="1"/>
+    <col min="6" max="7" width="4.28515625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" style="30" customWidth="1"/>
+    <col min="9" max="10" width="4.28515625" style="30" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" style="30" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="30" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="30" customWidth="1"/>
+    <col min="14" max="15" width="4.28515625" style="32" customWidth="1"/>
+    <col min="16" max="16" width="17.85546875" style="30" customWidth="1"/>
+    <col min="17" max="18" width="4.28515625" style="32" customWidth="1"/>
+    <col min="19" max="19" width="17.85546875" style="30" customWidth="1"/>
+    <col min="20" max="21" width="4.28515625" style="32" customWidth="1"/>
+    <col min="22" max="22" width="31.28515625" style="30" customWidth="1"/>
+    <col min="23" max="23" width="4.28515625" style="32" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="V1" s="32"/>
+    </row>
+    <row r="2" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="V2" s="32"/>
+    </row>
+    <row r="3" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="50"/>
+      <c r="M4" s="32"/>
+      <c r="P4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="V4" s="34"/>
+    </row>
+    <row r="5" spans="1:23" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="V5" s="32"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="V6" s="32"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D7" s="2"/>
+      <c r="E7" s="32"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="67"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="T8" s="2"/>
+      <c r="V8" s="23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D9" s="2"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D10" s="2"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="6"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B12" s="42"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="41"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="6"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B14" s="8"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="8"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="2"/>
+      <c r="V15" s="32"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C16" s="32"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="64"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B17" s="6"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="6"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B18" s="42"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="41"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="6"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="2"/>
+      <c r="V20" s="8"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="8"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="2"/>
+      <c r="V21" s="32"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D22" s="2"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="38"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="2"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B23" s="6"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="8"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="39"/>
+      <c r="V23" s="6"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="32"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="41"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="32"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="6"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B26" s="8"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="32"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="8"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="32"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="8"/>
+      <c r="V27" s="32"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C28" s="32"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="32"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="64"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B29" s="6"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="8"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="32"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="6"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B30" s="42"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="42"/>
+      <c r="V30" s="41"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B31" s="6"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="6"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B32" s="8"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="V32" s="8"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="8"/>
+      <c r="P33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="V33" s="32"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="38"/>
+      <c r="P34" s="32"/>
+      <c r="S34" s="32"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="8"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="U35" s="39"/>
+      <c r="V35" s="6"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B36" s="42"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="U36" s="42"/>
+      <c r="V36" s="41"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B37" s="6"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="6"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B38" s="8"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="32"/>
+      <c r="R38" s="39"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="39"/>
+      <c r="U38" s="42"/>
+      <c r="V38" s="8"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="32"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="8"/>
+      <c r="V39" s="32"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C40" s="32"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="32"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="39"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B41" s="6"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="O41" s="42"/>
+      <c r="P41" s="32"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="8"/>
+      <c r="U41" s="38"/>
+      <c r="V41" s="6"/>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B42" s="42"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="32"/>
+      <c r="R42" s="42"/>
+      <c r="S42" s="32"/>
+      <c r="U42" s="42"/>
+      <c r="V42" s="41"/>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+      <c r="C43" s="8"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="32"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="14"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="6"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B44" s="8"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="32"/>
+      <c r="V44" s="8"/>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="8"/>
+      <c r="S45" s="32"/>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="38"/>
+      <c r="S46" s="32"/>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B47" s="6"/>
+      <c r="C47" s="38"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="8"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="P47" s="8"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="32"/>
+      <c r="U47" s="39"/>
+      <c r="V47" s="6"/>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B48" s="42"/>
+      <c r="C48" s="41"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="O48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="42"/>
+      <c r="S48" s="32"/>
+      <c r="U48" s="42"/>
+      <c r="V48" s="41"/>
+    </row>
+    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B49" s="6"/>
+      <c r="C49" s="8"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="O49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="32"/>
+      <c r="U49" s="38"/>
+      <c r="V49" s="6"/>
+    </row>
+    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B50" s="8"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="R50" s="8"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="38"/>
+      <c r="U50" s="42"/>
+      <c r="V50" s="8"/>
+    </row>
+    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="P51" s="32"/>
+      <c r="R51" s="42"/>
+      <c r="S51" s="8"/>
+      <c r="V51" s="32"/>
+    </row>
+    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C52" s="32"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="6"/>
+      <c r="T52" s="38"/>
+    </row>
+    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B53" s="6"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="40"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="S53" s="8"/>
+      <c r="U53" s="38"/>
+      <c r="V53" s="6"/>
+    </row>
+    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B54" s="42"/>
+      <c r="C54" s="41"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="R54" s="19"/>
+      <c r="S54" s="18"/>
+      <c r="U54" s="42"/>
+      <c r="V54" s="41"/>
+    </row>
+    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B55" s="6"/>
+      <c r="C55" s="8"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="R55" s="19"/>
+      <c r="S55" s="18"/>
+      <c r="U55" s="38"/>
+      <c r="V55" s="6"/>
+    </row>
+    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B56" s="8"/>
+      <c r="C56" s="35"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="V56" s="8"/>
+    </row>
+    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="P57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="V57" s="32"/>
+    </row>
+    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="S58" s="32"/>
+    </row>
+    <row r="59" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B59" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="18"/>
+      <c r="V59" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W59" s="18"/>
+    </row>
+    <row r="60" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B60" s="6"/>
+      <c r="C60" s="38"/>
+      <c r="L60" s="32"/>
+      <c r="V60" s="37"/>
+    </row>
+    <row r="61" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B61" s="38"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="32"/>
+      <c r="L61" s="31"/>
+      <c r="O61" s="54"/>
+      <c r="P61" s="54"/>
+      <c r="Q61" s="54"/>
+      <c r="S61" s="32"/>
+      <c r="V61" s="39"/>
+      <c r="W61" s="18"/>
+    </row>
+    <row r="62" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B62" s="35"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="32"/>
+      <c r="O62" s="54"/>
+      <c r="P62" s="54"/>
+      <c r="Q62" s="54"/>
+      <c r="S62" s="32"/>
+      <c r="V62" s="36"/>
+    </row>
+    <row r="63" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B63" s="8"/>
+      <c r="V63" s="40"/>
+    </row>
+    <row r="64" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B64" s="32"/>
+      <c r="V64" s="32"/>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B65" s="32"/>
+      <c r="V65" s="32"/>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B66" s="32"/>
+      <c r="V66" s="32"/>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B67" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
+      <c r="N67" s="54"/>
+      <c r="O67" s="54"/>
+      <c r="P67" s="54"/>
+      <c r="Q67" s="54"/>
+      <c r="R67" s="54"/>
+      <c r="S67" s="32"/>
+      <c r="U67" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="V67" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B68" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="51"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="51"/>
+      <c r="N68" s="54"/>
+      <c r="O68" s="54"/>
+      <c r="P68" s="54"/>
+      <c r="Q68" s="54"/>
+      <c r="R68" s="54"/>
+      <c r="S68" s="32"/>
+      <c r="U68" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="V68" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B69" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="51"/>
+      <c r="N69" s="54"/>
+      <c r="O69" s="54"/>
+      <c r="P69" s="54"/>
+      <c r="Q69" s="54"/>
+      <c r="R69" s="54"/>
+      <c r="S69" s="32"/>
+      <c r="U69" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="V69" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B70" s="18"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="U70" s="19"/>
+      <c r="V70" s="18"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B71" s="18"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="P71" s="32"/>
+      <c r="S71" s="32"/>
+      <c r="U71" s="19"/>
+      <c r="V71" s="18"/>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="53"/>
+      <c r="M74" s="32"/>
+      <c r="P74" s="32"/>
+      <c r="R74" s="63"/>
+      <c r="S74" s="63"/>
+      <c r="T74" s="63"/>
+      <c r="U74" s="63"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+      <c r="M75" s="32"/>
+      <c r="S75" s="54"/>
+      <c r="T75" s="54"/>
+      <c r="U75" s="54"/>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="M76" s="32"/>
+      <c r="P76" s="32"/>
+      <c r="R76" s="63"/>
+      <c r="S76" s="63"/>
+      <c r="T76" s="63"/>
+      <c r="U76" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="H76:K76"/>
+    <mergeCell ref="O61:Q61"/>
+    <mergeCell ref="O62:Q62"/>
+    <mergeCell ref="N67:R67"/>
+    <mergeCell ref="N68:R68"/>
+    <mergeCell ref="N69:R69"/>
+    <mergeCell ref="R74:U74"/>
+    <mergeCell ref="S75:U75"/>
+    <mergeCell ref="R76:U76"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="H74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="K8:M8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="34" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>